--- a/MAJSushiConfig/ig/StructureDefinition-fr-adverse-event-document.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-fr-adverse-event-document.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-adverse-event-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-adverse-event-document</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:09:50+00:00</t>
+    <t>2026-09-07T10:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -625,7 +625,7 @@
     <t>AdverseEvent.resultingCondition</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-condition-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-condition-document|0.1.0)
 </t>
   </si>
   <si>
@@ -781,7 +781,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-medication-administration-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-administration-document|0.1.0)
 </t>
   </si>
   <si>
